--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\MOTORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724FF774-73CC-48E9-9227-8D92DA065798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74727D15-4A98-4CB8-A9BE-873F18DB34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="190">
   <si>
     <t>TAG</t>
   </si>
@@ -599,6 +599,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5684.JPG</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5641.JPG</t>
   </si>
 </sst>
 </file>
@@ -707,6 +713,36 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -797,36 +833,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -841,29 +847,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R71" headerRowDxfId="20" dataDxfId="19" totalsRowDxfId="18">
-  <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R71" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
+  <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="OS 5641 - 891527"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rolamentos" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rolamentos" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1101,7 +1113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57">
+    <row r="2" spans="1:18" ht="57" hidden="1">
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
@@ -1145,7 +1157,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="28.5">
+    <row r="3" spans="1:18" ht="42.75" hidden="1">
       <c r="A3" s="3" t="s">
         <v>44</v>
       </c>
@@ -1164,7 +1176,9 @@
       <c r="F3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>1760</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1173,14 +1187,18 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="28.5">
+      <c r="Q3" s="3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="42.75">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1210,14 +1228,16 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="28.5">
+    <row r="5" spans="1:18" ht="28.5" hidden="1">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -1254,7 +1274,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="28.5">
+    <row r="6" spans="1:18" ht="28.5" hidden="1">
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
@@ -1291,7 +1311,7 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="28.5">
+    <row r="7" spans="1:18" ht="28.5" hidden="1">
       <c r="A7" s="3" t="s">
         <v>66</v>
       </c>
@@ -1328,7 +1348,7 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="28.5">
+    <row r="8" spans="1:18" ht="28.5" hidden="1">
       <c r="A8" s="3" t="s">
         <v>70</v>
       </c>
@@ -1365,7 +1385,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="28.5">
+    <row r="9" spans="1:18" ht="28.5" hidden="1">
       <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
@@ -1402,7 +1422,7 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="28.5">
+    <row r="10" spans="1:18" ht="28.5" hidden="1">
       <c r="A10" s="3" t="s">
         <v>74</v>
       </c>
@@ -1439,7 +1459,7 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="28.5">
+    <row r="11" spans="1:18" ht="28.5" hidden="1">
       <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
@@ -1476,7 +1496,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="28.5">
+    <row r="12" spans="1:18" ht="28.5" hidden="1">
       <c r="A12" s="3" t="s">
         <v>81</v>
       </c>
@@ -1513,7 +1533,7 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="28.5">
+    <row r="13" spans="1:18" ht="28.5" hidden="1">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -1550,7 +1570,7 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="28.5">
+    <row r="14" spans="1:18" ht="28.5" hidden="1">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -1587,7 +1607,7 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="28.5">
+    <row r="15" spans="1:18" ht="28.5" hidden="1">
       <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
@@ -1622,7 +1642,7 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="28.5">
+    <row r="16" spans="1:18" ht="28.5" hidden="1">
       <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
@@ -1659,7 +1679,7 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
     </row>
-    <row r="17" spans="1:17" ht="28.5">
+    <row r="17" spans="1:17" ht="28.5" hidden="1">
       <c r="A17" s="3" t="s">
         <v>108</v>
       </c>
@@ -1692,7 +1712,7 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
     </row>
-    <row r="18" spans="1:17" ht="42.75">
+    <row r="18" spans="1:17" ht="42.75" hidden="1">
       <c r="A18" s="3" t="s">
         <v>110</v>
       </c>
@@ -1729,7 +1749,7 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="1:17" ht="28.5">
+    <row r="19" spans="1:17" ht="28.5" hidden="1">
       <c r="A19" s="3" t="s">
         <v>115</v>
       </c>
@@ -1766,7 +1786,7 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
     </row>
-    <row r="20" spans="1:17" ht="28.5">
+    <row r="20" spans="1:17" ht="28.5" hidden="1">
       <c r="A20" s="3" t="s">
         <v>118</v>
       </c>
@@ -1803,7 +1823,7 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:17" ht="28.5">
+    <row r="21" spans="1:17" ht="28.5" hidden="1">
       <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
@@ -1840,7 +1860,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17" ht="28.5">
+    <row r="22" spans="1:17" ht="28.5" hidden="1">
       <c r="A22" s="3" t="s">
         <v>125</v>
       </c>
@@ -1877,7 +1897,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="28.5">
+    <row r="23" spans="1:17" ht="28.5" hidden="1">
       <c r="A23" s="3" t="s">
         <v>130</v>
       </c>
@@ -1910,7 +1930,7 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:17" ht="28.5">
+    <row r="24" spans="1:17" ht="28.5" hidden="1">
       <c r="A24" s="3" t="s">
         <v>132</v>
       </c>
@@ -1947,7 +1967,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:17" ht="28.5">
+    <row r="25" spans="1:17" ht="28.5" hidden="1">
       <c r="A25" s="3" t="s">
         <v>137</v>
       </c>
@@ -1984,7 +2004,7 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
     </row>
-    <row r="26" spans="1:17" ht="28.5">
+    <row r="26" spans="1:17" ht="28.5" hidden="1">
       <c r="A26" s="3" t="s">
         <v>138</v>
       </c>
@@ -2019,7 +2039,7 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17" ht="28.5">
+    <row r="27" spans="1:17" ht="28.5" hidden="1">
       <c r="A27" s="3" t="s">
         <v>140</v>
       </c>
@@ -2056,7 +2076,7 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:17" ht="28.5">
+    <row r="28" spans="1:17" ht="28.5" hidden="1">
       <c r="A28" s="3" t="s">
         <v>143</v>
       </c>
@@ -2091,7 +2111,7 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:17" ht="28.5">
+    <row r="29" spans="1:17" ht="28.5" hidden="1">
       <c r="A29" s="3" t="s">
         <v>146</v>
       </c>
@@ -2128,7 +2148,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
     </row>
-    <row r="30" spans="1:17" ht="28.5">
+    <row r="30" spans="1:17" ht="28.5" hidden="1">
       <c r="A30" s="3" t="s">
         <v>148</v>
       </c>
@@ -2165,7 +2185,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:17" ht="28.5">
+    <row r="31" spans="1:17" ht="28.5" hidden="1">
       <c r="A31" s="3" t="s">
         <v>151</v>
       </c>
@@ -2202,7 +2222,7 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:17" ht="28.5">
+    <row r="32" spans="1:17" ht="28.5" hidden="1">
       <c r="A32" s="3" t="s">
         <v>153</v>
       </c>
@@ -2239,7 +2259,7 @@
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
     </row>
-    <row r="33" spans="1:17" ht="28.5">
+    <row r="33" spans="1:17" ht="28.5" hidden="1">
       <c r="A33" s="3" t="s">
         <v>157</v>
       </c>
@@ -2276,7 +2296,7 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="28.5">
+    <row r="34" spans="1:17" ht="28.5" hidden="1">
       <c r="A34" s="3" t="s">
         <v>158</v>
       </c>
@@ -2313,7 +2333,7 @@
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="28.5">
+    <row r="35" spans="1:17" ht="28.5" hidden="1">
       <c r="A35" s="3" t="s">
         <v>160</v>
       </c>
@@ -2350,7 +2370,7 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
     </row>
-    <row r="36" spans="1:17" ht="28.5">
+    <row r="36" spans="1:17" ht="28.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>165</v>
       </c>
@@ -2383,7 +2403,7 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
     </row>
-    <row r="37" spans="1:17" ht="28.5">
+    <row r="37" spans="1:17" ht="28.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
@@ -2420,7 +2440,7 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:17" ht="28.5">
+    <row r="38" spans="1:17" ht="28.5" hidden="1">
       <c r="A38" s="3" t="s">
         <v>172</v>
       </c>
@@ -2457,7 +2477,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:17" ht="28.5">
+    <row r="39" spans="1:17" ht="28.5" hidden="1">
       <c r="A39" s="3" t="s">
         <v>177</v>
       </c>
@@ -2494,7 +2514,7 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" spans="1:17" ht="28.5">
+    <row r="40" spans="1:17" ht="28.5" hidden="1">
       <c r="A40" s="3" t="s">
         <v>180</v>
       </c>
@@ -2523,7 +2543,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17" ht="28.5">
+    <row r="41" spans="1:17" ht="28.5" hidden="1">
       <c r="A41" s="3" t="s">
         <v>182</v>
       </c>
@@ -2560,7 +2580,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" hidden="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2579,7 +2599,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" hidden="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2598,7 +2618,7 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" hidden="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2617,7 +2637,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" hidden="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2636,7 +2656,7 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" hidden="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2655,7 +2675,7 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" hidden="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2674,7 +2694,7 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" hidden="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2693,7 +2713,7 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" hidden="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2712,7 +2732,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" hidden="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2731,7 +2751,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" hidden="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2750,7 +2770,7 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" hidden="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2769,7 +2789,7 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" hidden="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2788,7 +2808,7 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" hidden="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2807,7 +2827,7 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" hidden="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2826,7 +2846,7 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" hidden="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2845,7 +2865,7 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" hidden="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2864,7 +2884,7 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" hidden="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2883,7 +2903,7 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" hidden="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2902,7 +2922,7 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" hidden="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2921,7 +2941,7 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" hidden="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2940,7 +2960,7 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" hidden="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2959,7 +2979,7 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" hidden="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2978,7 +2998,7 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" hidden="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2997,7 +3017,7 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" hidden="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3016,7 +3036,7 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" hidden="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3035,7 +3055,7 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" hidden="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3054,7 +3074,7 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" hidden="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3073,7 +3093,7 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" hidden="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3092,7 +3112,7 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" hidden="1">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
@@ -3111,7 +3131,7 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" hidden="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -3133,13 +3153,13 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R71">
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\MOTORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74727D15-4A98-4CB8-A9BE-873F18DB34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ABE063-F308-4F1B-9C55-59946B6704A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,10 +601,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Ativos/img/OS5684.JPG</t>
-  </si>
-  <si>
-    <t>Ativos/img/OS5641.JPG</t>
+    <t>Ativos/img/OS5641.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5684.jpg</t>
   </si>
 </sst>
 </file>
@@ -851,7 +851,7 @@
   <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="OS 5641 - 891527"/>
+        <filter val="OS 5684 - 2394460"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1047,7 +1047,7 @@
     <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.875" style="2" customWidth="1"/>
@@ -1157,7 +1157,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="42.75" hidden="1">
+    <row r="3" spans="1:18" ht="28.5">
       <c r="A3" s="3" t="s">
         <v>44</v>
       </c>
@@ -1188,7 +1188,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -1198,7 +1198,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="42.75">
+    <row r="4" spans="1:18" ht="28.5" hidden="1">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1229,7 +1229,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\MOTORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ABE063-F308-4F1B-9C55-59946B6704A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{422367B1-3155-4625-B34E-327EFC04849A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="196">
   <si>
     <t>TAG</t>
   </si>
@@ -605,6 +605,24 @@
   </si>
   <si>
     <t>Ativos/img/OS5684.jpg</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1051,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -1185,15 +1203,27 @@
       <c r="I3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="L3" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="Q3" s="3">
         <v>231</v>
       </c>
@@ -3149,6 +3179,11 @@
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
       <c r="Q71" s="6"/>
+    </row>
+    <row r="90" spans="13:13">
+      <c r="M90" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\MOTORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{422367B1-3155-4625-B34E-327EFC04849A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86BCCF0-D6F8-47A6-8D61-C96184220640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="193">
   <si>
     <t>TAG</t>
   </si>
@@ -613,16 +613,7 @@
     <t>b</t>
   </si>
   <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>e</t>
-  </si>
-  <si>
-    <t>f</t>
   </si>
 </sst>
 </file>
@@ -866,13 +857,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R71" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="OS 5684 - 2394460"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
     <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
@@ -1131,7 +1116,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57" hidden="1">
+    <row r="2" spans="1:18" ht="57">
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
@@ -1175,7 +1160,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="28.5">
+    <row r="3" spans="1:18" ht="57">
       <c r="A3" s="3" t="s">
         <v>44</v>
       </c>
@@ -1213,22 +1198,22 @@
         <v>189</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>195</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="3">
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="28.5" hidden="1">
+    <row r="4" spans="1:18" ht="28.5">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1267,7 +1252,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="28.5" hidden="1">
+    <row r="5" spans="1:18" ht="28.5">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -1304,7 +1289,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="28.5" hidden="1">
+    <row r="6" spans="1:18" ht="28.5">
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
@@ -1341,7 +1326,7 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="28.5" hidden="1">
+    <row r="7" spans="1:18" ht="28.5">
       <c r="A7" s="3" t="s">
         <v>66</v>
       </c>
@@ -1378,7 +1363,7 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="28.5" hidden="1">
+    <row r="8" spans="1:18" ht="28.5">
       <c r="A8" s="3" t="s">
         <v>70</v>
       </c>
@@ -1415,7 +1400,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="28.5" hidden="1">
+    <row r="9" spans="1:18" ht="28.5">
       <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
@@ -1452,7 +1437,7 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="28.5" hidden="1">
+    <row r="10" spans="1:18" ht="28.5">
       <c r="A10" s="3" t="s">
         <v>74</v>
       </c>
@@ -1489,7 +1474,7 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="28.5" hidden="1">
+    <row r="11" spans="1:18" ht="28.5">
       <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
@@ -1526,7 +1511,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="28.5" hidden="1">
+    <row r="12" spans="1:18" ht="28.5">
       <c r="A12" s="3" t="s">
         <v>81</v>
       </c>
@@ -1563,7 +1548,7 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="28.5" hidden="1">
+    <row r="13" spans="1:18" ht="28.5">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -1600,7 +1585,7 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="28.5" hidden="1">
+    <row r="14" spans="1:18" ht="28.5">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -1637,7 +1622,7 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="28.5" hidden="1">
+    <row r="15" spans="1:18" ht="28.5">
       <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
@@ -1672,7 +1657,7 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="28.5" hidden="1">
+    <row r="16" spans="1:18" ht="28.5">
       <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
@@ -1709,7 +1694,7 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
     </row>
-    <row r="17" spans="1:17" ht="28.5" hidden="1">
+    <row r="17" spans="1:17" ht="28.5">
       <c r="A17" s="3" t="s">
         <v>108</v>
       </c>
@@ -1742,7 +1727,7 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
     </row>
-    <row r="18" spans="1:17" ht="42.75" hidden="1">
+    <row r="18" spans="1:17" ht="42.75">
       <c r="A18" s="3" t="s">
         <v>110</v>
       </c>
@@ -1779,7 +1764,7 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="1:17" ht="28.5" hidden="1">
+    <row r="19" spans="1:17" ht="28.5">
       <c r="A19" s="3" t="s">
         <v>115</v>
       </c>
@@ -1816,7 +1801,7 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
     </row>
-    <row r="20" spans="1:17" ht="28.5" hidden="1">
+    <row r="20" spans="1:17" ht="28.5">
       <c r="A20" s="3" t="s">
         <v>118</v>
       </c>
@@ -1853,7 +1838,7 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:17" ht="28.5" hidden="1">
+    <row r="21" spans="1:17" ht="28.5">
       <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
@@ -1890,7 +1875,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17" ht="28.5" hidden="1">
+    <row r="22" spans="1:17" ht="28.5">
       <c r="A22" s="3" t="s">
         <v>125</v>
       </c>
@@ -1927,7 +1912,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="28.5" hidden="1">
+    <row r="23" spans="1:17" ht="28.5">
       <c r="A23" s="3" t="s">
         <v>130</v>
       </c>
@@ -1960,7 +1945,7 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:17" ht="28.5" hidden="1">
+    <row r="24" spans="1:17" ht="28.5">
       <c r="A24" s="3" t="s">
         <v>132</v>
       </c>
@@ -1997,7 +1982,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:17" ht="28.5" hidden="1">
+    <row r="25" spans="1:17" ht="28.5">
       <c r="A25" s="3" t="s">
         <v>137</v>
       </c>
@@ -2034,7 +2019,7 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
     </row>
-    <row r="26" spans="1:17" ht="28.5" hidden="1">
+    <row r="26" spans="1:17" ht="28.5">
       <c r="A26" s="3" t="s">
         <v>138</v>
       </c>
@@ -2069,7 +2054,7 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17" ht="28.5" hidden="1">
+    <row r="27" spans="1:17" ht="28.5">
       <c r="A27" s="3" t="s">
         <v>140</v>
       </c>
@@ -2106,7 +2091,7 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:17" ht="28.5" hidden="1">
+    <row r="28" spans="1:17" ht="28.5">
       <c r="A28" s="3" t="s">
         <v>143</v>
       </c>
@@ -2141,7 +2126,7 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:17" ht="28.5" hidden="1">
+    <row r="29" spans="1:17" ht="28.5">
       <c r="A29" s="3" t="s">
         <v>146</v>
       </c>
@@ -2178,7 +2163,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
     </row>
-    <row r="30" spans="1:17" ht="28.5" hidden="1">
+    <row r="30" spans="1:17" ht="28.5">
       <c r="A30" s="3" t="s">
         <v>148</v>
       </c>
@@ -2215,7 +2200,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:17" ht="28.5" hidden="1">
+    <row r="31" spans="1:17" ht="28.5">
       <c r="A31" s="3" t="s">
         <v>151</v>
       </c>
@@ -2252,7 +2237,7 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:17" ht="28.5" hidden="1">
+    <row r="32" spans="1:17" ht="28.5">
       <c r="A32" s="3" t="s">
         <v>153</v>
       </c>
@@ -2289,7 +2274,7 @@
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
     </row>
-    <row r="33" spans="1:17" ht="28.5" hidden="1">
+    <row r="33" spans="1:17" ht="28.5">
       <c r="A33" s="3" t="s">
         <v>157</v>
       </c>
@@ -2326,7 +2311,7 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="28.5" hidden="1">
+    <row r="34" spans="1:17" ht="28.5">
       <c r="A34" s="3" t="s">
         <v>158</v>
       </c>
@@ -2363,7 +2348,7 @@
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="28.5" hidden="1">
+    <row r="35" spans="1:17" ht="28.5">
       <c r="A35" s="3" t="s">
         <v>160</v>
       </c>
@@ -2400,7 +2385,7 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
     </row>
-    <row r="36" spans="1:17" ht="28.5" hidden="1">
+    <row r="36" spans="1:17" ht="28.5">
       <c r="A36" s="3" t="s">
         <v>165</v>
       </c>
@@ -2433,7 +2418,7 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
     </row>
-    <row r="37" spans="1:17" ht="28.5" hidden="1">
+    <row r="37" spans="1:17" ht="28.5">
       <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
@@ -2470,7 +2455,7 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:17" ht="28.5" hidden="1">
+    <row r="38" spans="1:17" ht="28.5">
       <c r="A38" s="3" t="s">
         <v>172</v>
       </c>
@@ -2507,7 +2492,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:17" ht="28.5" hidden="1">
+    <row r="39" spans="1:17" ht="28.5">
       <c r="A39" s="3" t="s">
         <v>177</v>
       </c>
@@ -2544,7 +2529,7 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" spans="1:17" ht="28.5" hidden="1">
+    <row r="40" spans="1:17" ht="28.5">
       <c r="A40" s="3" t="s">
         <v>180</v>
       </c>
@@ -2573,7 +2558,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17" ht="28.5" hidden="1">
+    <row r="41" spans="1:17" ht="28.5">
       <c r="A41" s="3" t="s">
         <v>182</v>
       </c>
@@ -2610,7 +2595,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
     </row>
-    <row r="42" spans="1:17" hidden="1">
+    <row r="42" spans="1:17">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2629,7 +2614,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
     </row>
-    <row r="43" spans="1:17" hidden="1">
+    <row r="43" spans="1:17">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2648,7 +2633,7 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:17" hidden="1">
+    <row r="44" spans="1:17">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2667,7 +2652,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:17" hidden="1">
+    <row r="45" spans="1:17">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2686,7 +2671,7 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
     </row>
-    <row r="46" spans="1:17" hidden="1">
+    <row r="46" spans="1:17">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2705,7 +2690,7 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
     </row>
-    <row r="47" spans="1:17" hidden="1">
+    <row r="47" spans="1:17">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2724,7 +2709,7 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" spans="1:17" hidden="1">
+    <row r="48" spans="1:17">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2743,7 +2728,7 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" spans="1:17" hidden="1">
+    <row r="49" spans="1:17">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2762,7 +2747,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" spans="1:17" hidden="1">
+    <row r="50" spans="1:17">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2781,7 +2766,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" spans="1:17" hidden="1">
+    <row r="51" spans="1:17">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2800,7 +2785,7 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" spans="1:17" hidden="1">
+    <row r="52" spans="1:17">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2819,7 +2804,7 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" spans="1:17" hidden="1">
+    <row r="53" spans="1:17">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2838,7 +2823,7 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" spans="1:17" hidden="1">
+    <row r="54" spans="1:17">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2857,7 +2842,7 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
     </row>
-    <row r="55" spans="1:17" hidden="1">
+    <row r="55" spans="1:17">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2876,7 +2861,7 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
     </row>
-    <row r="56" spans="1:17" hidden="1">
+    <row r="56" spans="1:17">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2895,7 +2880,7 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
-    <row r="57" spans="1:17" hidden="1">
+    <row r="57" spans="1:17">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2914,7 +2899,7 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
     </row>
-    <row r="58" spans="1:17" hidden="1">
+    <row r="58" spans="1:17">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2933,7 +2918,7 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
     </row>
-    <row r="59" spans="1:17" hidden="1">
+    <row r="59" spans="1:17">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2952,7 +2937,7 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
     </row>
-    <row r="60" spans="1:17" hidden="1">
+    <row r="60" spans="1:17">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2971,7 +2956,7 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
     </row>
-    <row r="61" spans="1:17" hidden="1">
+    <row r="61" spans="1:17">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2990,7 +2975,7 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
     </row>
-    <row r="62" spans="1:17" hidden="1">
+    <row r="62" spans="1:17">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3009,7 +2994,7 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
-    <row r="63" spans="1:17" hidden="1">
+    <row r="63" spans="1:17">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3028,7 +3013,7 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
     </row>
-    <row r="64" spans="1:17" hidden="1">
+    <row r="64" spans="1:17">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3047,7 +3032,7 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
     </row>
-    <row r="65" spans="1:17" hidden="1">
+    <row r="65" spans="1:17">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3066,7 +3051,7 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" spans="1:17" hidden="1">
+    <row r="66" spans="1:17">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3085,7 +3070,7 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" spans="1:17" hidden="1">
+    <row r="67" spans="1:17">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3104,7 +3089,7 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" spans="1:17" hidden="1">
+    <row r="68" spans="1:17">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3123,7 +3108,7 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" spans="1:17" hidden="1">
+    <row r="69" spans="1:17">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3142,7 +3127,7 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70" spans="1:17" hidden="1">
+    <row r="70" spans="1:17">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
@@ -3161,7 +3146,7 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" hidden="1">
+    <row r="71" spans="1:17">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -3182,7 +3167,7 @@
     </row>
     <row r="90" spans="13:13">
       <c r="M90" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\MOTORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86BCCF0-D6F8-47A6-8D61-C96184220640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7629C18D-95EE-4245-9B8B-5C979AACEC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="312">
   <si>
     <t>TAG</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Quantidade_Oleo</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
     <t>Foto</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>https://SEU_USUARIO.github.io/NOME_REPOSITORIO/equipamentos/ME-631011/</t>
   </si>
   <si>
-    <t xml:space="preserve">WCG20 - V/F10 </t>
-  </si>
-  <si>
     <t>MOTOR 25 CV 3F 4 POLOS</t>
   </si>
   <si>
@@ -151,24 +145,9 @@
     <t>RELATORIO FINAL</t>
   </si>
   <si>
-    <t xml:space="preserve"> assets/pdf/RELATFINALOS5863.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> assets/pdf/OS5863.pdf</t>
-  </si>
-  <si>
     <t>WEG</t>
   </si>
   <si>
-    <t>OS 6251 - 1706589</t>
-  </si>
-  <si>
-    <t>Ativos/img/OS6217.JPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ativos/pdf/manualvertimax.pdf</t>
-  </si>
-  <si>
     <t>OS 5684 - 2394460</t>
   </si>
   <si>
@@ -598,22 +577,400 @@
     <t>30.947KG</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Ativos/img/OS5641.jpg</t>
   </si>
   <si>
     <t>Ativos/img/OS5684.jpg</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
     <t>e</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5684LP</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5701.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5715.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5740.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5790.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5628.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5742.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5604.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5718.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5666.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5681.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5792.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5615.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6268.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5454.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5400.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5721.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5630.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5704.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5743.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5607.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6238.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6066.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5411.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5669.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5653.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5636.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6144.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5674.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5846.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5891.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6163.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5223.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5774.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5391.jpg</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5397.jpg</t>
+  </si>
+  <si>
+    <t>80MP4</t>
+  </si>
+  <si>
+    <t>OS 5848 - 4821325</t>
+  </si>
+  <si>
+    <t>MOTOR 3 CV 3F 2 POLOS</t>
+  </si>
+  <si>
+    <t>90S/L</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS5848.jpg</t>
+  </si>
+  <si>
+    <t>COFCO INTERNATIONAL BRASIL S.A.</t>
+  </si>
+  <si>
+    <t>ADM DO BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>BUNGE ALIMENTOS S/A</t>
+  </si>
+  <si>
+    <t>CARGILL AGRICOLA S.A</t>
+  </si>
+  <si>
+    <t>DUAL DUARTE ALBUQUERQUE COM. E IND. LTDA</t>
+  </si>
+  <si>
+    <t>OLEOPLAN RONDONIA INDUSTRIA DE BIOCOMBUSTIVEL LTDA</t>
+  </si>
+  <si>
+    <t>RUMO MALHA NORTE S.A</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5225LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5848</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5397LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5391LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5774LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5223LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6163LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5891LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5846LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5674LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6144LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5636LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5653LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5669LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5411LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5641LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5790LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5701LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5715LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5740LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5628LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5742LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5604LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5718LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5666LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5681LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5792LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5615LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6268LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5454LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5400LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5721LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5630LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5704LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5743LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5607LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6238LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6066LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6232LP</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5641FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5701FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5715FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5740FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5790FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5628FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5742FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5604FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5684FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5718FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5666FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5681FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5792FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5615FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5400FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5721FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5630FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5704FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6268FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5454FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5743FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5607FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6238FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6066FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6232FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5411FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5669FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5653FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5636FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS6144FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5674FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5846FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5891FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS56163FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5223FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5774FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5391FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5397FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5225FA</t>
+  </si>
+  <si>
+    <t>Ativos/pdf/OS5848FA</t>
+  </si>
+  <si>
+    <t>Ativos/img/OS6232.jpg</t>
   </si>
 </sst>
 </file>
@@ -722,36 +1079,6 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -842,6 +1169,36 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -856,29 +1213,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R71" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R70" headerRowDxfId="20" dataDxfId="19" totalsRowDxfId="18">
+  <autoFilter ref="A1:R70" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="15">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rolamentos" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rolamentos" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Cliente" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1036,7 +1393,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -1083,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -1092,1507 +1449,1804 @@
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="42.75">
+      <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="57">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="3">
+        <v>1760</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="42.75">
+      <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="3" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="3">
-        <v>41.4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1750</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="3">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57">
-      <c r="A3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3520</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="42.75">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3540</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1760</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="28.5">
-      <c r="A4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="3">
-        <v>3520</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="L4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="M4" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="28.5">
+    <row r="5" spans="1:18" ht="42.75">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G5" s="3">
-        <v>3540</v>
+        <v>1780</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="28.5">
+    <row r="6" spans="1:18" ht="42.75">
       <c r="A6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3450</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1780</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="28.5">
+    <row r="7" spans="1:18" ht="42.75">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1765</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="3">
-        <v>3450</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="28.5">
+    <row r="8" spans="1:18" ht="42.75">
       <c r="A8" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="28.5">
+    <row r="9" spans="1:18" ht="42.75">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G9" s="3">
-        <v>1760</v>
+        <v>1735</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="P9" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="28.5">
+    <row r="10" spans="1:18" ht="42.75">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G10" s="3">
-        <v>1735</v>
+        <v>1175</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="28.5">
+    <row r="11" spans="1:18" ht="42.75">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3">
-        <v>1175</v>
+        <v>3540</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>255</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="28.5">
+    <row r="12" spans="1:18" ht="42.75">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3">
-        <v>3540</v>
+        <v>1750</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="28.5">
+    <row r="13" spans="1:18" ht="42.75">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3">
-        <v>1750</v>
+        <v>3520</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="P13" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="28.5">
+    <row r="14" spans="1:18" ht="42.75">
       <c r="A14" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3">
-        <v>3520</v>
+        <v>1690</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>86</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>258</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="28.5">
+    <row r="15" spans="1:18" ht="42.75">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3">
-        <v>1690</v>
+        <v>3500</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="Q15" s="3"/>
     </row>
     <row r="16" spans="1:18" ht="28.5">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>107</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G16" s="3">
-        <v>3500</v>
+        <v>1755</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="Q16" s="3"/>
     </row>
-    <row r="17" spans="1:17" ht="28.5">
+    <row r="17" spans="1:17" ht="42.75">
       <c r="A17" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="Q17" s="3"/>
     </row>
     <row r="18" spans="1:17" ht="42.75">
       <c r="A18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1715</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1750</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="1:17" ht="28.5">
+    <row r="19" spans="1:17" ht="42.75">
       <c r="A19" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3">
-        <v>1715</v>
+        <v>1155</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="Q19" s="3"/>
     </row>
-    <row r="20" spans="1:17" ht="28.5">
+    <row r="20" spans="1:17" ht="42.75">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G20" s="3">
-        <v>1155</v>
+        <v>3525</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:17" ht="28.5">
+    <row r="21" spans="1:17" ht="42.75">
       <c r="A21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1765</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="3">
-        <v>3525</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17" ht="28.5">
+    <row r="22" spans="1:17" ht="42.75">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G22" s="3">
-        <v>1765</v>
+        <v>1175</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="28.5">
+    <row r="23" spans="1:17" ht="42.75">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="F23" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G23" s="3">
-        <v>1175</v>
+        <v>1770</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>128</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="Q23" s="3"/>
     </row>
     <row r="24" spans="1:17" ht="28.5">
       <c r="A24" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
+      </c>
+      <c r="F24" s="3">
+        <v>440</v>
       </c>
       <c r="G24" s="3">
-        <v>1770</v>
+        <v>1760</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="K24" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="Q24" s="3"/>
     </row>
     <row r="25" spans="1:17" ht="28.5">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="3">
-        <v>440</v>
+        <v>132</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G25" s="3">
-        <v>1760</v>
+        <v>1740</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="K25" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="Q25" s="3"/>
     </row>
     <row r="26" spans="1:17" ht="28.5">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G26" s="3">
-        <v>1740</v>
+        <v>1760</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17" ht="28.5">
+    <row r="27" spans="1:17" ht="42.75">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G27" s="3">
         <v>1760</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="K27" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="P27" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:17" ht="28.5">
+    <row r="28" spans="1:17" ht="42.75">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
+      </c>
+      <c r="F28" s="3">
+        <v>380</v>
       </c>
       <c r="G28" s="3">
-        <v>1760</v>
+        <v>4440</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
+      <c r="P28" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:17" ht="28.5">
+    <row r="29" spans="1:17" ht="42.75">
       <c r="A29" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" s="3">
-        <v>380</v>
+        <v>142</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G29" s="3">
-        <v>4440</v>
+        <v>1725</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="Q29" s="3"/>
     </row>
-    <row r="30" spans="1:17" ht="28.5">
+    <row r="30" spans="1:17" ht="42.75">
       <c r="A30" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G30" s="3">
-        <v>1725</v>
+        <v>3515</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:17" ht="28.5">
+    <row r="31" spans="1:17" ht="42.75">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G31" s="3">
-        <v>3515</v>
+        <v>1750</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="P31" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:17" ht="28.5">
+    <row r="32" spans="1:17" ht="42.75">
       <c r="A32" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G32" s="3">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="Q32" s="3"/>
     </row>
-    <row r="33" spans="1:17" ht="28.5">
+    <row r="33" spans="1:17" ht="71.25">
       <c r="A33" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G33" s="3">
-        <v>1725</v>
+        <v>3505</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
+      <c r="P33" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="Q33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="28.5">
+    <row r="34" spans="1:17" ht="57">
       <c r="A34" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G34" s="3">
-        <v>3505</v>
+        <v>1175</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="Q34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="28.5">
+    <row r="35" spans="1:17" ht="42.75">
       <c r="A35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1765</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1175</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
+      <c r="P35" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="Q35" s="3"/>
     </row>
     <row r="36" spans="1:17" ht="28.5">
       <c r="A36" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1770</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="I36" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
+      <c r="P36" s="3" t="s">
+        <v>305</v>
+      </c>
       <c r="Q36" s="3"/>
     </row>
     <row r="37" spans="1:17" ht="28.5">
       <c r="A37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1710</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1770</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
+      <c r="P37" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:17" ht="28.5">
+    <row r="38" spans="1:17" ht="42.75">
       <c r="A38" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1710</v>
-      </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
+      <c r="P38" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:17" ht="28.5">
+    <row r="39" spans="1:17" ht="42.75">
       <c r="A39" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>186</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
+      <c r="P39" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="Q39" s="3"/>
     </row>
     <row r="40" spans="1:17" ht="28.5">
       <c r="A40" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="E40" s="3" t="s">
-        <v>181</v>
+        <v>90</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="G40" s="3">
+        <v>3550</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
+      <c r="P40" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17" ht="28.5">
+    <row r="41" spans="1:17" ht="71.25">
       <c r="A41" s="3" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G41" s="3">
-        <v>3550</v>
+        <v>3470</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
+      <c r="P41" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="Q41" s="3"/>
     </row>
     <row r="42" spans="1:17">
@@ -3109,36 +3763,36 @@
       <c r="Q68" s="3"/>
     </row>
     <row r="69" spans="1:17">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="6"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
+      <c r="Q69" s="6"/>
     </row>
     <row r="70" spans="1:17">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
-      <c r="K70" s="6"/>
+      <c r="K70" s="7"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -3146,40 +3800,21 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="6"/>
-    </row>
-    <row r="90" spans="13:13">
-      <c r="M90" s="2" t="s">
-        <v>192</v>
+    <row r="89" spans="13:13">
+      <c r="M89" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B72:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <conditionalFormatting sqref="B71:B1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R71">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  <conditionalFormatting sqref="R2:R70">
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -3200,82 +3835,82 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
